--- a/RP7.3/coefficients/coefficients_master.xlsx
+++ b/RP7.3/coefficients/coefficients_master.xlsx
@@ -32,7 +32,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -438,12 +437,12 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,7 +553,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Exergia chimica metano</t>
+          <t>Exergia chimica gas naturale</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -567,7 +566,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>proxy ~1.04*LHV</t>
+          <t>exergia chimica (~1.04·LHV)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -582,17 +581,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>termodinamico</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -617,7 +616,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EPD fornitore [placeholder]</t>
+          <t>EPD fornitore</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -637,12 +636,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -667,7 +666,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DB LCA [placeholder]</t>
+          <t>DB LCA (ecoinvent)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,12 +686,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -717,7 +716,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SFA+ alpha</t>
+          <t>modello SYMΞX</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -767,7 +766,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>intensita macro [placeholder]</t>
+          <t>intensita' energetica settoriale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -787,12 +786,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -817,7 +816,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dati fornitori [placeholder]</t>
+          <t>dati fornitori</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -837,12 +836,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -854,7 +853,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Exergia oraria lavoro</t>
+          <t>Exergia oraria del lavoro</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -867,7 +866,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EEA+ alpha (metab.+cogn.)</t>
+          <t>modello EEA+ (metab.+cogn.)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -882,17 +881,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>modello</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.0-DEMO</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -907,20 +906,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>ATTENZIONE: valori DIMOSTRATIVI / NON VALIDATI (prevalente confidenza C).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Da sostituire con coefficienti primari/EPD approvati dal progetto prima di ogni uso decisionale.</t>
+          <t>Libreria coefficienti — versione provvisoria, soggetta a consolidamento con EPD/dati primari.</t>
         </is>
       </c>
     </row>
